--- a/data/week03/coach_training_load.xlsx
+++ b/data/week03/coach_training_load.xlsx
@@ -1942,7 +1942,7 @@
         <v/>
       </c>
       <c r="AA19">
-        <f>SUM([4:[18)</f>
+        <f>SUM(AA4:AA18)</f>
         <v/>
       </c>
     </row>
